--- a/docs/CFS_Span_Table.xlsx
+++ b/docs/CFS_Span_Table.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CadWork4\Desktop\AI\CFS Span Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55811378-1C35-4547-A2C8-C695712B51E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75014FBE-434E-4E68-9162-ADAFE79C9BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P (kN)" sheetId="1" r:id="rId1"/>
     <sheet name="Mx (kN-m)" sheetId="2" r:id="rId2"/>
+    <sheet name="Vy (kN)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
   <si>
     <t>Section</t>
   </si>
@@ -110,6 +111,15 @@
     <t>G550 50020N</t>
   </si>
   <si>
+    <t>G550 63020N</t>
+  </si>
+  <si>
+    <t>G550 63020NS1</t>
+  </si>
+  <si>
+    <t>G550 63020NS2</t>
+  </si>
+  <si>
     <t>G550 270115N</t>
   </si>
   <si>
@@ -164,13 +174,7 @@
     <t>Superspan 650x180x2.95</t>
   </si>
   <si>
-    <t>G550 63020N</t>
-  </si>
-  <si>
-    <t>G550 63020NS1</t>
-  </si>
-  <si>
-    <t>G550 63020NS2</t>
+    <t>Vy(kN)</t>
   </si>
 </sst>
 </file>
@@ -838,7 +842,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>572.5</v>
@@ -918,7 +922,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>921.35</v>
@@ -998,7 +1002,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>1707.7</v>
@@ -1078,7 +1082,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>207.25</v>
@@ -1158,7 +1162,7 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>148.72</v>
@@ -1238,7 +1242,7 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>151.05000000000001</v>
@@ -1318,7 +1322,7 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>61.341999999999999</v>
@@ -1398,7 +1402,7 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>142.13999999999999</v>
@@ -1478,7 +1482,7 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>303.87</v>
@@ -1558,7 +1562,7 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B14">
         <v>207.25</v>
@@ -1638,7 +1642,7 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15">
         <v>105.64</v>
@@ -1718,7 +1722,7 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16">
         <v>240.05</v>
@@ -1798,7 +1802,7 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B17">
         <v>236.38</v>
@@ -1878,7 +1882,7 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>49.177999999999997</v>
@@ -1958,7 +1962,7 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B19">
         <v>103.2</v>
@@ -2038,7 +2042,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20">
         <v>1932.6</v>
@@ -2118,7 +2122,7 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B21">
         <v>2563.8000000000002</v>
@@ -2198,7 +2202,7 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>1303.7</v>
@@ -2278,7 +2282,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>2397</v>
@@ -2358,7 +2362,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>3055.6</v>
@@ -2438,7 +2442,7 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B25">
         <v>1751.2</v>
@@ -2851,7 +2855,7 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>155.37</v>
@@ -2931,7 +2935,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>259.56</v>
@@ -3011,7 +3015,7 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>387.1</v>
@@ -3091,7 +3095,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>24.786000000000001</v>
@@ -3171,7 +3175,7 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>13.227</v>
@@ -3251,7 +3255,7 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>14.971</v>
@@ -3331,7 +3335,7 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>7.5824999999999996</v>
@@ -3411,7 +3415,7 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>16.488</v>
@@ -3491,7 +3495,7 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>33.581000000000003</v>
@@ -3571,7 +3575,7 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B14">
         <v>24.766999999999999</v>
@@ -3651,7 +3655,7 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15">
         <v>20.128</v>
@@ -3731,7 +3735,7 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16">
         <v>43.628</v>
@@ -3811,7 +3815,7 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B17">
         <v>41.652999999999999</v>
@@ -3891,7 +3895,7 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B18">
         <v>2.6158999999999999</v>
@@ -3971,7 +3975,7 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B19">
         <v>5.0727000000000002</v>
@@ -4051,7 +4055,7 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20">
         <v>341.64</v>
@@ -4131,7 +4135,7 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B21">
         <v>464.36</v>
@@ -4211,7 +4215,7 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B22">
         <v>219.96</v>
@@ -4291,7 +4295,7 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B23">
         <v>634.1</v>
@@ -4371,7 +4375,7 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B24">
         <v>825.82</v>
@@ -4451,7 +4455,7 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B25">
         <v>446.73</v>
@@ -4527,6 +4531,220 @@
       </c>
       <c r="Z25">
         <v>402.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2">
+        <v>72.915000000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3">
+        <v>117.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>248.76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5">
+        <v>338.18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6">
+        <v>259.56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>429.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>138.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9">
+        <v>48.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10">
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11">
+        <v>11.619</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12">
+        <v>45.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13">
+        <v>90.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <v>138.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15">
+        <v>39.61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <v>79.61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17">
+        <v>79.23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18">
+        <v>16.928999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19">
+        <v>40.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20">
+        <v>389.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21">
+        <v>389.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22">
+        <v>389.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24">
+        <v>1277.5999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25">
+        <v>946.5</v>
       </c>
     </row>
   </sheetData>
